--- a/public/downloads/marketing-plan-e9b5c3.xlsx
+++ b/public/downloads/marketing-plan-e9b5c3.xlsx
@@ -8,13 +8,14 @@
     <sheet sheetId="2" name="90-Day Marketing Plan" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Lead Sources" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Competitor Analysis" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="📊 Lead Tracker" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="235">
   <si>
     <t>📋 HOW TO USE: 90-Day Marketing Plan</t>
   </si>
@@ -665,6 +666,60 @@
   </si>
   <si>
     <t>What's your unique selling proposition (USP)?</t>
+  </si>
+  <si>
+    <t>📊 LEAD TRACKER — YOUR SALES PIPELINE</t>
+  </si>
+  <si>
+    <t>Log every lead, track status, and watch your pipeline grow. This is your simple CRM — use it religiously.</t>
+  </si>
+  <si>
+    <t>Project Type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes / Follow-Up</t>
+  </si>
+  <si>
+    <t>PIPELINE SUMMARY</t>
+  </si>
+  <si>
+    <t>New Leads</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>Estimates Sent</t>
+  </si>
+  <si>
+    <t>Won</t>
+  </si>
+  <si>
+    <t>Lost</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>PIPELINE VALUE</t>
+  </si>
+  <si>
+    <t>Total Pipeline Value</t>
+  </si>
+  <si>
+    <t>Won Revenue</t>
+  </si>
+  <si>
+    <t>Pending Value</t>
+  </si>
+  <si>
+    <t>Average Deal Size</t>
+  </si>
+  <si>
+    <t>💡 Follow up on 'Estimate Sent' leads within 48 hours — that's when close rates drop off a cliff.</t>
   </si>
 </sst>
 </file>
@@ -674,7 +729,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -742,8 +797,21 @@
       <b/>
       <color rgb="FFF59E0B"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2563EB"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -763,6 +831,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -793,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -832,6 +910,12 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3244,4 +3328,709 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF10B981"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>8</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>10</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>11</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>14</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>15</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>16</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>17</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>19</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>20</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>21</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>22</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>23</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>24</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="16">
+        <v>25</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="16">
+        <v>26</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>27</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>28</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>29</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>30</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
+        <v>31</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <v>32</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
+        <v>33</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>34</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="16">
+        <v>35</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>36</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
+        <v>37</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="16">
+        <v>38</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <v>39</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="16">
+        <v>40</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="28">
+        <f>COUNTA(D5:D44)</f>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="28">
+        <f>COUNTIF(G5:G44,"New Lead")</f>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="28">
+        <f>COUNTIF(G5:G44,"Contacted")</f>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="28">
+        <f>COUNTIF(G5:G44,"Estimate Sent")</f>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="28">
+        <f>COUNTIF(G5:G44,"Won")</f>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C52" s="28">
+        <f>COUNTIF(G5:G44,"Lost")</f>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="28">
+        <f>COUNTIF(G5:G44,"On Hold")</f>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C55" s="29"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="C56" s="30">
+        <f>SUMIF(G5:G44,"&lt;&gt;Lost",F5:F44)</f>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C57" s="31">
+        <f>SUMIF(G5:G44,"Won",F5:F44)</f>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="30">
+        <f>SUMIFS(F5:F44,G5:G44,"New Lead")+SUMIFS(F5:F44,G5:G44,"Contacted")+SUMIFS(F5:F44,G5:G44,"Estimate Sent")</f>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="C59" s="30">
+        <f>IF(COUNTA(F5:F44)&gt;0,AVERAGEIF(F5:F44,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="32">
+        <f>IF(COUNTIF(G5:G44,"Won")+COUNTIF(G5:G44,"Lost")&gt;0,COUNTIF(G5:G44,"Won")/(COUNTIF(G5:G44,"Won")+COUNTIF(G5:G44,"Lost")),0)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A63:H63"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C44">
+      <formula1>"Google Search,Google Ads,Facebook,Nextdoor,Referral,Yard Sign,Door Hanger,Angi,Yelp,Website,Cold Call,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C5:C44">
+      <formula1>"Google Search,Google Ads,Facebook,Nextdoor,Referral,Yard Sign,Door Hanger,Angi,Yelp,Website,Cold Call,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E44">
+      <formula1>"Driveway,Patio,Slab,Foundation,Stamped,Sidewalk,Retaining Wall,Repair,Steps,Pool Deck,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E5:E44">
+      <formula1>"Driveway,Patio,Slab,Foundation,Stamped,Sidewalk,Retaining Wall,Repair,Steps,Pool Deck,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G44">
+      <formula1>"New Lead,Contacted,Estimate Sent,Won,Lost,On Hold"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G5:G44">
+      <formula1>"New Lead,Contacted,Estimate Sent,Won,Lost,On Hold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
 </file>
--- a/public/downloads/marketing-plan-e9b5c3.xlsx
+++ b/public/downloads/marketing-plan-e9b5c3.xlsx
@@ -7,14 +7,15 @@
     <sheet sheetId="1" name="📋 How to Use" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="90-Day Marketing Plan" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Lead Sources" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Competitor Analysis" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="Lead Tracker" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Competitor Analysis" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="229">
   <si>
     <t>📋 HOW TO USE: 90-Day Marketing Plan</t>
   </si>
@@ -626,6 +627,42 @@
   </si>
   <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>LEAD TRACKER</t>
+  </si>
+  <si>
+    <t>Log every lead — track from first contact to won/lost. Know your pipeline at a glance.</t>
+  </si>
+  <si>
+    <t>Project Type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>PIPELINE SUMMARY</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>New Leads</t>
+  </si>
+  <si>
+    <t>Quoted</t>
+  </si>
+  <si>
+    <t>Won</t>
+  </si>
+  <si>
+    <t>Lost</t>
+  </si>
+  <si>
+    <t>Pipeline Value (Quoted)</t>
+  </si>
+  <si>
+    <t>Won Revenue</t>
   </si>
   <si>
     <t>LOCAL COMPETITOR ANALYSIS</t>
@@ -793,7 +830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -831,6 +868,8 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2985,6 +3024,684 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>8</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>10</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>11</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>14</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>15</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>16</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>17</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>19</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>20</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>21</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>22</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>23</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>24</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="16">
+        <v>25</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="16">
+        <v>26</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>27</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>28</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>29</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>30</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
+        <v>31</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <v>32</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
+        <v>33</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>34</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="16">
+        <v>35</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>36</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
+        <v>37</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="16">
+        <v>38</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <v>39</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="16">
+        <v>40</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C48" s="20">
+        <f>COUNTA(D5:D44)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="C49" s="20">
+        <f>COUNTIF(G5:G44,"New")</f>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="C50" s="20">
+        <f>COUNTIF(G5:G44,"Quoted")</f>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="20">
+        <f>COUNTIF(G5:G44,"Won")</f>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" s="20">
+        <f>COUNTIF(G5:G44,"Lost")</f>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="27">
+        <f>SUMIFS(F5:F44,G5:G44,"Quoted")</f>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C54" s="27">
+        <f>SUMIFS(F5:F44,G5:G44,"Won")</f>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="28">
+        <f>IF(COUNTA(D5:D44)&gt;0,COUNTIF(G5:G44,"Won")/COUNTA(D5:D44),0)</f>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A47:H47"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C44">
+      <formula1>"Google,Google Ads,Facebook,Nextdoor,Referral,Yard Sign,Door Hanger,Angi,HomeAdvisor,Yelp,Website,Cold Call,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C5:C44">
+      <formula1>"Google,Google Ads,Facebook,Nextdoor,Referral,Yard Sign,Door Hanger,Angi,HomeAdvisor,Yelp,Website,Cold Call,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E44">
+      <formula1>"Driveway,Patio,Slab,Foundation,Stamped,Sidewalk,Repair,Steps,Retaining Wall,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E5:E44">
+      <formula1>"Driveway,Patio,Slab,Foundation,Stamped,Sidewalk,Repair,Steps,Retaining Wall,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G44">
+      <formula1>"New,Contacted,Quoted,Won,Lost,No Response"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G5:G44">
+      <formula1>"New,Contacted,Quoted,Won,Lost,No Response"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2998,7 +3715,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3009,7 +3726,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -3023,22 +3740,22 @@
         <v>181</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>202</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3153,7 +3870,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -3163,55 +3880,55 @@
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
+      <c r="A17" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="21"/>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="21"/>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
+      <c r="A20" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
+      <c r="A21" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>

--- a/public/downloads/marketing-plan-e9b5c3.xlsx
+++ b/public/downloads/marketing-plan-e9b5c3.xlsx
@@ -9,13 +9,14 @@
     <sheet sheetId="3" name="Lead Sources" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Lead Tracker" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Competitor Analysis" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="📊 Lead Tracker" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="240">
   <si>
     <t>📋 HOW TO USE: 90-Day Marketing Plan</t>
   </si>
@@ -702,6 +703,39 @@
   </si>
   <si>
     <t>What's your unique selling proposition (USP)?</t>
+  </si>
+  <si>
+    <t>📊 LEAD TRACKER — YOUR SALES PIPELINE</t>
+  </si>
+  <si>
+    <t>Log every lead, track status, and watch your pipeline grow. This is your simple CRM — use it religiously.</t>
+  </si>
+  <si>
+    <t>Notes / Follow-Up</t>
+  </si>
+  <si>
+    <t>Contacted</t>
+  </si>
+  <si>
+    <t>Estimates Sent</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>PIPELINE VALUE</t>
+  </si>
+  <si>
+    <t>Total Pipeline Value</t>
+  </si>
+  <si>
+    <t>Pending Value</t>
+  </si>
+  <si>
+    <t>Average Deal Size</t>
+  </si>
+  <si>
+    <t>💡 Follow up on 'Estimate Sent' leads within 48 hours — that's when close rates drop off a cliff.</t>
   </si>
 </sst>
 </file>
@@ -711,7 +745,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -779,8 +813,21 @@
       <b/>
       <color rgb="FFF59E0B"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF2563EB"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -800,6 +847,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -830,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -871,6 +928,12 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3961,4 +4024,709 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF10B981"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="16">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>8</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>10</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>11</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>14</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>15</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>16</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>17</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>19</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>20</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>21</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>22</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>23</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>24</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="16">
+        <v>25</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="16">
+        <v>26</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>27</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>28</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>29</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>30</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
+        <v>31</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <v>32</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
+        <v>33</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>34</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="16">
+        <v>35</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>36</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
+        <v>37</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="16">
+        <v>38</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <v>39</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="16">
+        <v>40</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="30">
+        <f>COUNTA(D5:D44)</f>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="30">
+        <f>COUNTIF(G5:G44,"New Lead")</f>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="C49" s="30">
+        <f>COUNTIF(G5:G44,"Contacted")</f>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" s="30">
+        <f>COUNTIF(G5:G44,"Estimate Sent")</f>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="30">
+        <f>COUNTIF(G5:G44,"Won")</f>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" s="30">
+        <f>COUNTIF(G5:G44,"Lost")</f>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="30">
+        <f>COUNTIF(G5:G44,"On Hold")</f>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="C55" s="31"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C56" s="32">
+        <f>SUMIF(G5:G44,"&lt;&gt;Lost",F5:F44)</f>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" s="33">
+        <f>SUMIF(G5:G44,"Won",F5:F44)</f>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="32">
+        <f>SUMIFS(F5:F44,G5:G44,"New Lead")+SUMIFS(F5:F44,G5:G44,"Contacted")+SUMIFS(F5:F44,G5:G44,"Estimate Sent")</f>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="C59" s="32">
+        <f>IF(COUNTA(F5:F44)&gt;0,AVERAGEIF(F5:F44,"&gt;0"),0)</f>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="34">
+        <f>IF(COUNTIF(G5:G44,"Won")+COUNTIF(G5:G44,"Lost")&gt;0,COUNTIF(G5:G44,"Won")/(COUNTIF(G5:G44,"Won")+COUNTIF(G5:G44,"Lost")),0)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A63:H63"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C44">
+      <formula1>"Google Search,Google Ads,Facebook,Nextdoor,Referral,Yard Sign,Door Hanger,Angi,Yelp,Website,Cold Call,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C5:C44">
+      <formula1>"Google Search,Google Ads,Facebook,Nextdoor,Referral,Yard Sign,Door Hanger,Angi,Yelp,Website,Cold Call,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E44">
+      <formula1>"Driveway,Patio,Slab,Foundation,Stamped,Sidewalk,Retaining Wall,Repair,Steps,Pool Deck,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E5:E44">
+      <formula1>"Driveway,Patio,Slab,Foundation,Stamped,Sidewalk,Retaining Wall,Repair,Steps,Pool Deck,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G44">
+      <formula1>"New Lead,Contacted,Estimate Sent,Won,Lost,On Hold"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G5:G44">
+      <formula1>"New Lead,Contacted,Estimate Sent,Won,Lost,On Hold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
 </file>